--- a/data/db/subsystems.xlsx
+++ b/data/db/subsystems.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C623"/>
+  <dimension ref="A1:D623"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -430,7 +430,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>rfcc_status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>rfwcc_status</t>
         </is>
       </c>
     </row>
@@ -450,6 +455,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -467,6 +477,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -484,6 +499,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -501,6 +521,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D5" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -518,6 +543,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D6" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -535,6 +565,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D7" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -552,6 +587,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D8" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -569,6 +609,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D9" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -586,6 +631,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -603,6 +653,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D11" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -620,6 +675,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D12" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -637,6 +697,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -654,6 +719,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D14" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -671,6 +741,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D15" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -688,6 +763,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D16" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -705,6 +785,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D17" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -722,6 +807,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -739,6 +829,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D19" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -756,6 +851,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D20" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -773,6 +873,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D21" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -790,6 +895,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D22" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -807,6 +917,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D23" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -824,6 +939,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D24" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -841,6 +961,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D25" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -858,6 +983,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D26" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -875,6 +1005,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D27" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -892,6 +1027,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D28" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -909,6 +1049,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D29" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -926,6 +1071,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D30" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -943,6 +1093,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D31" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -960,6 +1115,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D32" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -977,6 +1137,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D33" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -994,6 +1159,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D34" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1011,6 +1181,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D35" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -1028,6 +1203,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D36" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -1045,6 +1225,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1062,6 +1247,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D38" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -1079,6 +1269,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D39" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -1096,6 +1291,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D40" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -1113,6 +1313,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D41" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -1130,6 +1335,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D42" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -1147,6 +1357,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D43" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -1164,6 +1379,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D44" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -1181,6 +1401,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D45" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
@@ -1198,6 +1423,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D46" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1215,6 +1445,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D47" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1232,6 +1467,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D48" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
@@ -1249,6 +1489,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D49" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1266,6 +1511,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D50" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1283,6 +1533,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D51" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1300,6 +1555,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D52" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1317,6 +1577,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D53" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -1334,6 +1599,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D54" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1351,6 +1621,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D55" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
@@ -1368,6 +1643,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D56" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
@@ -1385,6 +1665,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D57" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1402,6 +1687,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D58" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
@@ -1419,6 +1709,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D59" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1436,6 +1731,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D60" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
@@ -1453,6 +1753,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D61" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
@@ -1470,6 +1775,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D62" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
@@ -1487,6 +1797,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D63" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1504,6 +1819,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D64" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1521,6 +1841,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D65" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
@@ -1538,6 +1863,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D66" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
@@ -1555,6 +1885,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D67" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
@@ -1572,6 +1907,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D68" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
@@ -1589,6 +1929,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D69" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
@@ -1606,6 +1951,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D70" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
@@ -1623,6 +1973,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D71" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
@@ -1640,6 +1995,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D72" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
@@ -1657,6 +2017,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D73" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
@@ -1674,6 +2039,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D74" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
@@ -1691,6 +2061,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D75" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
@@ -1708,6 +2083,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D76" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
@@ -1725,6 +2105,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D77" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
@@ -1742,6 +2127,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D78" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
@@ -1759,6 +2149,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D79" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -1776,6 +2171,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D80" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
@@ -1793,6 +2193,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D81" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
@@ -1810,6 +2215,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D82" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -1827,6 +2237,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D83" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -1844,6 +2259,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D84" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
@@ -1861,6 +2281,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D85" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
@@ -1878,6 +2303,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D86" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
@@ -1895,6 +2325,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D87" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
@@ -1912,6 +2347,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D88" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
@@ -1929,6 +2369,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D89" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
@@ -1946,6 +2391,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D90" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
@@ -1963,6 +2413,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D91" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
@@ -1980,6 +2435,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D92" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
@@ -1997,6 +2457,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D93" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
@@ -2014,6 +2479,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D94" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -2031,6 +2501,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D95" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -2048,6 +2523,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D96" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
@@ -2065,6 +2545,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D97" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -2082,6 +2567,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D98" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
@@ -2099,6 +2589,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D99" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
@@ -2116,6 +2611,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D100" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -2133,6 +2633,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D101" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
@@ -2150,6 +2655,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D102" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
@@ -2167,6 +2677,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D103" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -2184,6 +2699,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D104" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -2201,6 +2721,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D105" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
@@ -2218,6 +2743,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D106" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
@@ -2235,6 +2765,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D107" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -2252,6 +2787,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D108" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
@@ -2269,6 +2809,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D109" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
@@ -2286,6 +2831,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D110" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
@@ -2303,6 +2853,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D111" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
@@ -2320,6 +2875,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D112" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
@@ -2337,6 +2897,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D113" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
@@ -2354,6 +2919,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D114" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
@@ -2371,6 +2941,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D115" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -2388,6 +2963,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D116" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
@@ -2405,6 +2985,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D117" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
@@ -2422,6 +3007,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D118" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
@@ -2439,6 +3029,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D119" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
@@ -2456,6 +3051,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D120" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
@@ -2473,6 +3073,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D121" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2490,6 +3095,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D122" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
@@ -2507,6 +3117,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D123" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2524,6 +3139,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D124" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
@@ -2541,6 +3161,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D125" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
@@ -2558,6 +3183,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D126" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
@@ -2575,6 +3205,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D127" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
@@ -2592,6 +3227,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D128" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -2609,6 +3249,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D129" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
@@ -2626,6 +3271,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D130" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
@@ -2643,6 +3293,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D131" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
@@ -2660,6 +3315,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D132" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -2677,6 +3337,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D133" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
@@ -2694,6 +3359,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D134" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
@@ -2711,6 +3381,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D135" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
@@ -2728,6 +3403,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D136" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
@@ -2745,6 +3425,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D137" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
@@ -2762,6 +3447,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D138" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
@@ -2779,6 +3469,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D139" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
@@ -2796,6 +3491,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D140" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
@@ -2813,6 +3513,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D141" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
@@ -2830,6 +3535,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D142" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
@@ -2847,6 +3557,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D143" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
@@ -2864,6 +3579,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D144" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
@@ -2881,6 +3601,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D145" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
@@ -2898,6 +3623,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D146" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
@@ -2915,6 +3645,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D147" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -2932,6 +3667,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D148" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
@@ -2949,6 +3689,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D149" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
@@ -2966,6 +3711,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D150" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
@@ -2983,6 +3733,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D151" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
@@ -3000,6 +3755,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D152" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
@@ -3017,6 +3777,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D153" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
@@ -3034,6 +3799,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D154" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
@@ -3051,6 +3821,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D155" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
@@ -3068,6 +3843,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D156" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="inlineStr">
@@ -3085,6 +3865,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D157" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="inlineStr">
@@ -3102,6 +3887,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D158" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="inlineStr">
@@ -3119,6 +3909,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D159" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="inlineStr">
@@ -3136,6 +3931,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D160" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="inlineStr">
@@ -3153,6 +3953,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D161" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="1" t="inlineStr">
@@ -3170,6 +3975,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D162" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="inlineStr">
@@ -3187,6 +3997,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D163" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="inlineStr">
@@ -3204,6 +4019,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D164" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -3221,6 +4041,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D165" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="inlineStr">
@@ -3238,6 +4063,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D166" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="inlineStr">
@@ -3255,6 +4085,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D167" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -3272,6 +4107,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D168" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="1" t="inlineStr">
@@ -3289,6 +4129,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D169" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -3306,6 +4151,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D170" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="inlineStr">
@@ -3323,6 +4173,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D171" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="1" t="inlineStr">
@@ -3340,6 +4195,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D172" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -3357,6 +4217,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D173" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="inlineStr">
@@ -3374,6 +4239,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D174" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="inlineStr">
@@ -3391,6 +4261,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D175" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -3408,6 +4283,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D176" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -3425,6 +4305,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D177" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -3442,6 +4327,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D178" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -3459,6 +4349,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D179" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="inlineStr">
@@ -3476,6 +4371,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D180" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="inlineStr">
@@ -3493,6 +4393,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D181" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="inlineStr">
@@ -3510,6 +4415,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D182" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="inlineStr">
@@ -3527,6 +4437,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D183" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="inlineStr">
@@ -3544,6 +4459,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D184" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="1" t="inlineStr">
@@ -3561,6 +4481,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D185" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="inlineStr">
@@ -3578,6 +4503,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D186" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="inlineStr">
@@ -3595,6 +4525,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D187" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="1" t="inlineStr">
@@ -3612,6 +4547,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D188" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="inlineStr">
@@ -3629,6 +4569,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D189" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="inlineStr">
@@ -3646,6 +4591,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D190" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="inlineStr">
@@ -3663,6 +4613,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D191" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -3680,6 +4635,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D192" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -3697,6 +4657,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D193" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -3714,6 +4679,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D194" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -3731,6 +4701,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D195" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -3748,6 +4723,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D196" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="inlineStr">
@@ -3765,6 +4745,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D197" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="inlineStr">
@@ -3782,6 +4767,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D198" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="inlineStr">
@@ -3799,6 +4789,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D199" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="inlineStr">
@@ -3816,6 +4811,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D200" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="inlineStr">
@@ -3833,6 +4833,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D201" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="inlineStr">
@@ -3850,6 +4855,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D202" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="inlineStr">
@@ -3867,6 +4877,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D203" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="inlineStr">
@@ -3884,6 +4899,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D204" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="inlineStr">
@@ -3901,6 +4921,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D205" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="1" t="inlineStr">
@@ -3918,6 +4943,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D206" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -3935,6 +4965,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D207" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="inlineStr">
@@ -3952,6 +4987,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D208" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="inlineStr">
@@ -3969,6 +5009,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D209" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="1" t="inlineStr">
@@ -3986,6 +5031,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D210" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -4003,6 +5053,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D211" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -4020,6 +5075,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -4037,6 +5097,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D213" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="inlineStr">
@@ -4054,6 +5119,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D214" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="inlineStr">
@@ -4071,6 +5141,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D215" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="inlineStr">
@@ -4088,6 +5163,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D216" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="inlineStr">
@@ -4105,6 +5185,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D217" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="inlineStr">
@@ -4122,6 +5207,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D218" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -4139,6 +5229,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D219" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="inlineStr">
@@ -4156,6 +5251,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D220" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="inlineStr">
@@ -4173,6 +5273,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D221" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="1" t="inlineStr">
@@ -4190,6 +5295,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D222" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="inlineStr">
@@ -4207,6 +5317,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D223" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="inlineStr">
@@ -4224,6 +5339,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D224" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="inlineStr">
@@ -4241,6 +5361,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D225" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="inlineStr">
@@ -4258,6 +5383,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D226" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="1" t="inlineStr">
@@ -4275,6 +5405,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D227" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="inlineStr">
@@ -4292,6 +5427,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D228" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="inlineStr">
@@ -4309,6 +5449,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D229" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="inlineStr">
@@ -4326,6 +5471,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D230" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="1" t="inlineStr">
@@ -4343,6 +5493,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D231" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="1" t="inlineStr">
@@ -4360,6 +5515,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D232" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="1" t="inlineStr">
@@ -4377,6 +5537,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D233" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="inlineStr">
@@ -4394,6 +5559,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D234" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="inlineStr">
@@ -4411,6 +5581,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D235" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="inlineStr">
@@ -4428,6 +5603,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D236" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="inlineStr">
@@ -4445,6 +5625,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D237" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="inlineStr">
@@ -4462,6 +5647,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D238" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" s="1" t="inlineStr">
@@ -4479,6 +5669,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D239" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="inlineStr">
@@ -4496,6 +5691,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D240" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="inlineStr">
@@ -4513,6 +5713,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D241" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="inlineStr">
@@ -4530,6 +5735,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D242" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="inlineStr">
@@ -4547,6 +5757,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D243" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="inlineStr">
@@ -4564,6 +5779,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="inlineStr">
@@ -4581,6 +5801,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D245" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="inlineStr">
@@ -4598,6 +5823,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D246" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="inlineStr">
@@ -4615,6 +5845,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D247" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="inlineStr">
@@ -4632,6 +5867,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D248" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="inlineStr">
@@ -4649,6 +5889,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D249" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="inlineStr">
@@ -4666,6 +5911,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D250" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="1" t="inlineStr">
@@ -4683,6 +5933,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D251" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="inlineStr">
@@ -4700,6 +5955,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D252" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="inlineStr">
@@ -4717,6 +5977,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D253" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" s="1" t="inlineStr">
@@ -4734,6 +5999,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D254" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="inlineStr">
@@ -4751,6 +6021,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D255" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="inlineStr">
@@ -4768,6 +6043,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D256" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="inlineStr">
@@ -4785,6 +6065,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D257" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="inlineStr">
@@ -4802,6 +6087,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D258" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="inlineStr">
@@ -4819,6 +6109,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D259" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="inlineStr">
@@ -4836,6 +6131,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D260" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="1" t="inlineStr">
@@ -4853,6 +6153,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D261" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="inlineStr">
@@ -4870,6 +6175,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D262" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="inlineStr">
@@ -4887,6 +6197,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D263" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="inlineStr">
@@ -4904,6 +6219,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D264" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="inlineStr">
@@ -4921,6 +6241,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D265" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="1" t="inlineStr">
@@ -4938,6 +6263,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D266" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="inlineStr">
@@ -4955,6 +6285,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D267" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="inlineStr">
@@ -4972,6 +6307,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D268" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="inlineStr">
@@ -4989,6 +6329,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D269" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="inlineStr">
@@ -5006,6 +6351,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D270" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="inlineStr">
@@ -5023,6 +6373,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D271" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="inlineStr">
@@ -5040,6 +6395,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D272" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="inlineStr">
@@ -5057,6 +6417,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D273" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="inlineStr">
@@ -5074,6 +6439,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D274" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="inlineStr">
@@ -5091,6 +6461,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D275" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="1" t="inlineStr">
@@ -5108,6 +6483,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D276" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="inlineStr">
@@ -5125,6 +6505,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D277" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="inlineStr">
@@ -5142,6 +6527,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D278" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="inlineStr">
@@ -5159,6 +6549,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D279" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="inlineStr">
@@ -5176,6 +6571,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D280" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="inlineStr">
@@ -5193,6 +6593,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D281" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="inlineStr">
@@ -5210,6 +6615,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D282" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="inlineStr">
@@ -5227,6 +6637,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D283" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="inlineStr">
@@ -5244,6 +6659,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D284" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="inlineStr">
@@ -5261,6 +6681,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D285" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="inlineStr">
@@ -5278,6 +6703,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D286" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="inlineStr">
@@ -5295,6 +6725,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D287" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="inlineStr">
@@ -5312,6 +6747,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D288" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="inlineStr">
@@ -5329,6 +6769,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D289" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" s="1" t="inlineStr">
@@ -5346,6 +6791,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D290" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="inlineStr">
@@ -5363,6 +6813,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D291" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="inlineStr">
@@ -5380,6 +6835,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D292" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="inlineStr">
@@ -5397,6 +6857,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D293" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="inlineStr">
@@ -5414,6 +6879,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D294" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="inlineStr">
@@ -5431,6 +6901,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D295" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="inlineStr">
@@ -5448,6 +6923,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D296" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="inlineStr">
@@ -5465,6 +6945,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D297" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="1" t="inlineStr">
@@ -5482,6 +6967,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D298" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="inlineStr">
@@ -5499,6 +6989,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D299" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="inlineStr">
@@ -5516,6 +7011,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D300" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="inlineStr">
@@ -5533,6 +7033,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D301" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="1" t="inlineStr">
@@ -5550,6 +7055,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D302" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="inlineStr">
@@ -5567,6 +7077,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D303" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="inlineStr">
@@ -5584,6 +7099,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D304" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="inlineStr">
@@ -5601,6 +7121,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D305" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="inlineStr">
@@ -5618,6 +7143,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D306" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="inlineStr">
@@ -5635,6 +7165,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D307" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="inlineStr">
@@ -5652,6 +7187,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D308" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="inlineStr">
@@ -5669,6 +7209,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D309" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="inlineStr">
@@ -5686,6 +7231,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D310" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="inlineStr">
@@ -5703,6 +7253,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D311" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="inlineStr">
@@ -5720,6 +7275,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D312" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="inlineStr">
@@ -5737,6 +7297,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D313" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="inlineStr">
@@ -5754,6 +7319,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D314" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="inlineStr">
@@ -5771,6 +7341,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D315" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="inlineStr">
@@ -5788,6 +7363,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D316" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="inlineStr">
@@ -5805,6 +7385,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D317" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" s="1" t="inlineStr">
@@ -5822,6 +7407,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D318" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="inlineStr">
@@ -5839,6 +7429,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D319" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="inlineStr">
@@ -5856,6 +7451,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D320" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="inlineStr">
@@ -5873,6 +7473,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D321" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="inlineStr">
@@ -5890,6 +7495,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D322" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="inlineStr">
@@ -5907,6 +7517,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D323" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="inlineStr">
@@ -5924,6 +7539,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D324" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="inlineStr">
@@ -5941,6 +7561,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D325" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="inlineStr">
@@ -5958,6 +7583,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D326" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="inlineStr">
@@ -5975,6 +7605,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D327" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="inlineStr">
@@ -5992,6 +7627,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D328" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="inlineStr">
@@ -6009,6 +7649,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D329" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="inlineStr">
@@ -6026,6 +7671,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D330" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="inlineStr">
@@ -6043,6 +7693,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D331" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="inlineStr">
@@ -6060,6 +7715,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D332" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="inlineStr">
@@ -6077,6 +7737,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D333" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="inlineStr">
@@ -6094,6 +7759,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D334" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="inlineStr">
@@ -6111,6 +7781,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D335" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="inlineStr">
@@ -6128,6 +7803,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D336" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="inlineStr">
@@ -6145,6 +7825,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D337" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="inlineStr">
@@ -6162,6 +7847,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D338" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="inlineStr">
@@ -6179,6 +7869,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D339" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="inlineStr">
@@ -6196,6 +7891,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D340" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="inlineStr">
@@ -6213,6 +7913,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D341" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="inlineStr">
@@ -6230,6 +7935,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D342" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="inlineStr">
@@ -6247,6 +7957,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D343" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="inlineStr">
@@ -6264,6 +7979,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D344" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="inlineStr">
@@ -6281,6 +8001,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D345" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="inlineStr">
@@ -6298,6 +8023,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D346" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="inlineStr">
@@ -6315,6 +8045,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D347" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="inlineStr">
@@ -6332,6 +8067,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D348" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="inlineStr">
@@ -6349,6 +8089,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D349" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="inlineStr">
@@ -6366,6 +8111,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D350" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="inlineStr">
@@ -6383,6 +8133,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D351" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="inlineStr">
@@ -6400,6 +8155,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D352" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="1" t="inlineStr">
@@ -6417,6 +8177,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D353" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="inlineStr">
@@ -6434,6 +8199,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D354" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="inlineStr">
@@ -6451,6 +8221,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D355" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="inlineStr">
@@ -6468,6 +8243,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D356" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="inlineStr">
@@ -6485,6 +8265,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D357" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="1" t="inlineStr">
@@ -6502,6 +8287,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D358" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="inlineStr">
@@ -6519,6 +8309,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D359" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="inlineStr">
@@ -6536,6 +8331,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D360" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="inlineStr">
@@ -6553,6 +8353,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D361" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="1" t="inlineStr">
@@ -6570,6 +8375,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D362" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="inlineStr">
@@ -6587,6 +8397,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D363" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="inlineStr">
@@ -6604,6 +8419,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D364" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="inlineStr">
@@ -6621,6 +8441,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D365" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="1" t="inlineStr">
@@ -6638,6 +8463,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D366" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="inlineStr">
@@ -6655,6 +8485,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D367" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="inlineStr">
@@ -6672,6 +8507,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D368" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="inlineStr">
@@ -6689,6 +8529,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D369" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="inlineStr">
@@ -6706,6 +8551,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D370" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="inlineStr">
@@ -6723,6 +8573,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D371" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="inlineStr">
@@ -6740,6 +8595,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D372" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="inlineStr">
@@ -6757,6 +8617,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D373" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="1" t="inlineStr">
@@ -6774,6 +8639,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D374" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="inlineStr">
@@ -6791,6 +8661,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D375" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="inlineStr">
@@ -6808,6 +8683,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D376" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="inlineStr">
@@ -6825,6 +8705,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D377" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="inlineStr">
@@ -6842,6 +8727,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D378" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="inlineStr">
@@ -6859,6 +8749,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D379" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="inlineStr">
@@ -6876,6 +8771,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D380" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="inlineStr">
@@ -6893,6 +8793,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D381" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="inlineStr">
@@ -6910,6 +8815,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D382" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="inlineStr">
@@ -6927,6 +8837,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D383" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="inlineStr">
@@ -6944,6 +8859,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D384" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" s="1" t="inlineStr">
@@ -6961,6 +8881,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D385" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="inlineStr">
@@ -6978,6 +8903,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D386" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" s="1" t="inlineStr">
@@ -6995,6 +8925,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D387" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="inlineStr">
@@ -7012,6 +8947,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D388" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="inlineStr">
@@ -7029,6 +8969,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D389" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="inlineStr">
@@ -7046,6 +8991,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D390" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="inlineStr">
@@ -7063,6 +9013,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D391" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" s="1" t="inlineStr">
@@ -7080,6 +9035,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D392" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="inlineStr">
@@ -7097,6 +9057,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D393" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="inlineStr">
@@ -7114,6 +9079,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D394" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="inlineStr">
@@ -7131,6 +9101,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D395" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="inlineStr">
@@ -7148,6 +9123,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D396" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="inlineStr">
@@ -7165,6 +9145,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D397" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="inlineStr">
@@ -7182,6 +9167,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D398" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" s="1" t="inlineStr">
@@ -7199,6 +9189,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D399" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="inlineStr">
@@ -7216,6 +9211,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D400" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="inlineStr">
@@ -7233,6 +9233,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D401" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="inlineStr">
@@ -7250,6 +9255,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D402" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="inlineStr">
@@ -7267,6 +9277,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D403" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="inlineStr">
@@ -7284,6 +9299,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D404" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="inlineStr">
@@ -7301,6 +9321,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D405" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="inlineStr">
@@ -7318,6 +9343,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D406" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="1" t="inlineStr">
@@ -7335,6 +9365,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D407" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="inlineStr">
@@ -7352,6 +9387,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D408" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="inlineStr">
@@ -7369,6 +9409,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D409" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="inlineStr">
@@ -7386,6 +9431,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D410" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="1" t="inlineStr">
@@ -7403,6 +9453,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D411" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="inlineStr">
@@ -7420,6 +9475,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D412" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="inlineStr">
@@ -7437,6 +9497,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D413" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="1" t="inlineStr">
@@ -7454,6 +9519,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D414" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="inlineStr">
@@ -7471,6 +9541,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D415" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="inlineStr">
@@ -7488,6 +9563,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D416" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="inlineStr">
@@ -7505,6 +9585,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D417" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="inlineStr">
@@ -7522,6 +9607,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D418" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="inlineStr">
@@ -7539,6 +9629,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D419" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="inlineStr">
@@ -7556,6 +9651,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D420" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="inlineStr">
@@ -7573,6 +9673,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D421" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="inlineStr">
@@ -7590,6 +9695,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D422" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="inlineStr">
@@ -7607,6 +9717,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D423" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="inlineStr">
@@ -7624,6 +9739,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D424" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="inlineStr">
@@ -7641,6 +9761,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D425" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="inlineStr">
@@ -7658,6 +9783,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D426" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="inlineStr">
@@ -7675,6 +9805,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D427" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="inlineStr">
@@ -7692,6 +9827,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D428" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="inlineStr">
@@ -7709,6 +9849,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D429" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="inlineStr">
@@ -7726,6 +9871,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D430" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="inlineStr">
@@ -7743,6 +9893,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D431" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" s="1" t="inlineStr">
@@ -7760,6 +9915,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D432" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="inlineStr">
@@ -7777,6 +9937,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D433" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="inlineStr">
@@ -7794,6 +9959,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D434" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="inlineStr">
@@ -7811,6 +9981,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D435" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="inlineStr">
@@ -7828,6 +10003,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D436" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="inlineStr">
@@ -7845,6 +10025,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D437" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="inlineStr">
@@ -7862,6 +10047,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D438" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" s="1" t="inlineStr">
@@ -7879,6 +10069,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D439" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="inlineStr">
@@ -7896,6 +10091,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D440" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="inlineStr">
@@ -7913,6 +10113,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D441" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="inlineStr">
@@ -7930,6 +10135,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D442" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="inlineStr">
@@ -7947,6 +10157,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D443" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="inlineStr">
@@ -7964,6 +10179,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D444" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="inlineStr">
@@ -7981,6 +10201,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D445" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="inlineStr">
@@ -7998,6 +10223,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D446" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="inlineStr">
@@ -8015,6 +10245,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D447" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="inlineStr">
@@ -8032,6 +10267,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D448" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="inlineStr">
@@ -8049,6 +10289,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D449" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="inlineStr">
@@ -8066,6 +10311,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D450" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="inlineStr">
@@ -8083,6 +10333,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D451" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="452">
       <c r="A452" s="1" t="inlineStr">
@@ -8100,6 +10355,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D452" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="inlineStr">
@@ -8117,6 +10377,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D453" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="inlineStr">
@@ -8134,6 +10399,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D454" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="inlineStr">
@@ -8151,6 +10421,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D455" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="inlineStr">
@@ -8168,6 +10443,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D456" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="inlineStr">
@@ -8185,6 +10465,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D457" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="inlineStr">
@@ -8202,6 +10487,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D458" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="1" t="inlineStr">
@@ -8219,6 +10509,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D459" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" s="1" t="inlineStr">
@@ -8236,6 +10531,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D460" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="inlineStr">
@@ -8253,6 +10553,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D461" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="inlineStr">
@@ -8270,6 +10575,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D462" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="inlineStr">
@@ -8287,6 +10597,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D463" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="1" t="inlineStr">
@@ -8304,6 +10619,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D464" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="1" t="inlineStr">
@@ -8321,6 +10641,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D465" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="466">
       <c r="A466" s="1" t="inlineStr">
@@ -8338,6 +10663,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D466" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="1" t="inlineStr">
@@ -8355,6 +10685,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D467" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="inlineStr">
@@ -8372,6 +10707,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D468" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="inlineStr">
@@ -8389,6 +10729,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D469" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="1" t="inlineStr">
@@ -8406,6 +10751,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D470" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="inlineStr">
@@ -8423,6 +10773,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D471" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="472">
       <c r="A472" s="1" t="inlineStr">
@@ -8440,6 +10795,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D472" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="473">
       <c r="A473" s="1" t="inlineStr">
@@ -8457,6 +10817,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D473" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="inlineStr">
@@ -8474,6 +10839,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D474" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="inlineStr">
@@ -8491,6 +10861,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D475" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="inlineStr">
@@ -8508,6 +10883,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D476" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="inlineStr">
@@ -8525,6 +10905,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D477" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="inlineStr">
@@ -8542,6 +10927,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D478" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="inlineStr">
@@ -8559,6 +10949,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D479" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="inlineStr">
@@ -8576,6 +10971,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D480" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="inlineStr">
@@ -8593,6 +10993,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D481" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="inlineStr">
@@ -8610,6 +11015,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D482" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="inlineStr">
@@ -8627,6 +11037,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D483" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="inlineStr">
@@ -8644,6 +11059,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D484" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="inlineStr">
@@ -8661,6 +11081,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D485" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="inlineStr">
@@ -8678,6 +11103,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D486" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="487">
       <c r="A487" s="1" t="inlineStr">
@@ -8695,6 +11125,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D487" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="inlineStr">
@@ -8712,6 +11147,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D488" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="inlineStr">
@@ -8729,6 +11169,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D489" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="inlineStr">
@@ -8746,6 +11191,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D490" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="1" t="inlineStr">
@@ -8763,6 +11213,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D491" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="inlineStr">
@@ -8780,6 +11235,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D492" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="inlineStr">
@@ -8797,6 +11257,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D493" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" s="1" t="inlineStr">
@@ -8814,6 +11279,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D494" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="inlineStr">
@@ -8831,6 +11301,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D495" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="inlineStr">
@@ -8848,6 +11323,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D496" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="inlineStr">
@@ -8865,6 +11345,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D497" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="498">
       <c r="A498" s="1" t="inlineStr">
@@ -8882,6 +11367,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D498" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="499">
       <c r="A499" s="1" t="inlineStr">
@@ -8899,6 +11389,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D499" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="1" t="inlineStr">
@@ -8916,6 +11411,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D500" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="1" t="inlineStr">
@@ -8933,6 +11433,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D501" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="1" t="inlineStr">
@@ -8950,6 +11455,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D502" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="1" t="inlineStr">
@@ -8967,6 +11477,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D503" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="1" t="inlineStr">
@@ -8984,6 +11499,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D504" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="1" t="inlineStr">
@@ -9001,6 +11521,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D505" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="1" t="inlineStr">
@@ -9018,6 +11543,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D506" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="1" t="inlineStr">
@@ -9035,6 +11565,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D507" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="1" t="inlineStr">
@@ -9052,6 +11587,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D508" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="509">
       <c r="A509" s="1" t="inlineStr">
@@ -9069,6 +11609,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D509" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="1" t="inlineStr">
@@ -9086,6 +11631,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D510" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="1" t="inlineStr">
@@ -9103,6 +11653,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D511" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="1" t="inlineStr">
@@ -9120,6 +11675,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D512" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="1" t="inlineStr">
@@ -9137,6 +11697,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D513" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="1" t="inlineStr">
@@ -9154,6 +11719,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D514" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="1" t="inlineStr">
@@ -9171,6 +11741,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D515" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="1" t="inlineStr">
@@ -9188,6 +11763,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D516" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="1" t="inlineStr">
@@ -9205,6 +11785,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D517" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="1" t="inlineStr">
@@ -9222,6 +11807,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D518" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="1" t="inlineStr">
@@ -9239,6 +11829,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D519" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="520">
       <c r="A520" s="1" t="inlineStr">
@@ -9256,6 +11851,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D520" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="521">
       <c r="A521" s="1" t="inlineStr">
@@ -9273,6 +11873,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D521" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="522">
       <c r="A522" s="1" t="inlineStr">
@@ -9290,6 +11895,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D522" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="1" t="inlineStr">
@@ -9307,6 +11917,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D523" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="524">
       <c r="A524" s="1" t="inlineStr">
@@ -9324,6 +11939,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D524" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="525">
       <c r="A525" s="1" t="inlineStr">
@@ -9341,6 +11961,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D525" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="1" t="inlineStr">
@@ -9358,6 +11983,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D526" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="1" t="inlineStr">
@@ -9375,6 +12005,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D527" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="528">
       <c r="A528" s="1" t="inlineStr">
@@ -9392,6 +12027,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D528" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="1" t="inlineStr">
@@ -9409,6 +12049,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D529" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="530">
       <c r="A530" s="1" t="inlineStr">
@@ -9426,6 +12071,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D530" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="1" t="inlineStr">
@@ -9443,6 +12093,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D531" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="1" t="inlineStr">
@@ -9460,6 +12115,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D532" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="533">
       <c r="A533" s="1" t="inlineStr">
@@ -9477,6 +12137,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D533" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="534">
       <c r="A534" s="1" t="inlineStr">
@@ -9494,6 +12159,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D534" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="535">
       <c r="A535" s="1" t="inlineStr">
@@ -9511,6 +12181,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D535" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="536">
       <c r="A536" s="1" t="inlineStr">
@@ -9528,6 +12203,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D536" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="537">
       <c r="A537" s="1" t="inlineStr">
@@ -9545,6 +12225,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D537" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="538">
       <c r="A538" s="1" t="inlineStr">
@@ -9562,6 +12247,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D538" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" s="1" t="inlineStr">
@@ -9579,6 +12269,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D539" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" s="1" t="inlineStr">
@@ -9596,6 +12291,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D540" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" s="1" t="inlineStr">
@@ -9613,6 +12313,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D541" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="542">
       <c r="A542" s="1" t="inlineStr">
@@ -9630,6 +12335,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D542" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="1" t="inlineStr">
@@ -9647,6 +12357,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D543" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="544">
       <c r="A544" s="1" t="inlineStr">
@@ -9664,6 +12379,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D544" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="545">
       <c r="A545" s="1" t="inlineStr">
@@ -9681,6 +12401,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D545" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" s="1" t="inlineStr">
@@ -9698,6 +12423,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D546" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="547">
       <c r="A547" s="1" t="inlineStr">
@@ -9715,6 +12445,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D547" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="1" t="inlineStr">
@@ -9732,6 +12467,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D548" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" s="1" t="inlineStr">
@@ -9749,6 +12489,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D549" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" s="1" t="inlineStr">
@@ -9766,6 +12511,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D550" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" s="1" t="inlineStr">
@@ -9783,6 +12533,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D551" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="552">
       <c r="A552" s="1" t="inlineStr">
@@ -9800,6 +12555,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D552" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="1" t="inlineStr">
@@ -9817,6 +12577,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D553" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="554">
       <c r="A554" s="1" t="inlineStr">
@@ -9834,6 +12599,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D554" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="1" t="inlineStr">
@@ -9851,6 +12621,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D555" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="556">
       <c r="A556" s="1" t="inlineStr">
@@ -9868,6 +12643,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D556" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="557">
       <c r="A557" s="1" t="inlineStr">
@@ -9885,6 +12665,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D557" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="558">
       <c r="A558" s="1" t="inlineStr">
@@ -9902,6 +12687,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D558" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="1" t="inlineStr">
@@ -9919,6 +12709,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D559" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="560">
       <c r="A560" s="1" t="inlineStr">
@@ -9936,6 +12731,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D560" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="561">
       <c r="A561" s="1" t="inlineStr">
@@ -9953,6 +12753,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D561" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="562">
       <c r="A562" s="1" t="inlineStr">
@@ -9970,6 +12775,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D562" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="563">
       <c r="A563" s="1" t="inlineStr">
@@ -9987,6 +12797,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D563" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="564">
       <c r="A564" s="1" t="inlineStr">
@@ -10004,6 +12819,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D564" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="1" t="inlineStr">
@@ -10021,6 +12841,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D565" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="566">
       <c r="A566" s="1" t="inlineStr">
@@ -10038,6 +12863,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D566" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="567">
       <c r="A567" s="1" t="inlineStr">
@@ -10055,6 +12885,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D567" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="568">
       <c r="A568" s="1" t="inlineStr">
@@ -10072,6 +12907,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D568" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="569">
       <c r="A569" s="1" t="inlineStr">
@@ -10089,6 +12929,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D569" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="1" t="inlineStr">
@@ -10106,6 +12951,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D570" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" s="1" t="inlineStr">
@@ -10123,6 +12973,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D571" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="1" t="inlineStr">
@@ -10140,6 +12995,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D572" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" s="1" t="inlineStr">
@@ -10157,6 +13017,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D573" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="1" t="inlineStr">
@@ -10174,6 +13039,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D574" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="1" t="inlineStr">
@@ -10191,6 +13061,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D575" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="1" t="inlineStr">
@@ -10208,6 +13083,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D576" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" s="1" t="inlineStr">
@@ -10225,6 +13105,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D577" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" s="1" t="inlineStr">
@@ -10242,6 +13127,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D578" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" s="1" t="inlineStr">
@@ -10259,6 +13149,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D579" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="1" t="inlineStr">
@@ -10276,6 +13171,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D580" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="1" t="inlineStr">
@@ -10293,6 +13193,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D581" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="1" t="inlineStr">
@@ -10310,6 +13215,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D582" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="1" t="inlineStr">
@@ -10327,6 +13237,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D583" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="1" t="inlineStr">
@@ -10344,6 +13259,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D584" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="585">
       <c r="A585" s="1" t="inlineStr">
@@ -10361,6 +13281,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D585" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="1" t="inlineStr">
@@ -10378,6 +13303,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D586" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="587">
       <c r="A587" s="1" t="inlineStr">
@@ -10395,6 +13325,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D587" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="588">
       <c r="A588" s="1" t="inlineStr">
@@ -10412,6 +13347,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D588" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="589">
       <c r="A589" s="1" t="inlineStr">
@@ -10429,6 +13369,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D589" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="590">
       <c r="A590" s="1" t="inlineStr">
@@ -10446,6 +13391,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D590" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" s="1" t="inlineStr">
@@ -10463,6 +13413,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D591" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="592">
       <c r="A592" s="1" t="inlineStr">
@@ -10480,6 +13435,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D592" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" s="1" t="inlineStr">
@@ -10497,6 +13457,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D593" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" s="1" t="inlineStr">
@@ -10514,6 +13479,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D594" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" s="1" t="inlineStr">
@@ -10531,6 +13501,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D595" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="596">
       <c r="A596" s="1" t="inlineStr">
@@ -10548,6 +13523,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D596" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="597">
       <c r="A597" s="1" t="inlineStr">
@@ -10565,6 +13545,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D597" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="1" t="inlineStr">
@@ -10582,6 +13567,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D598" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="599">
       <c r="A599" s="1" t="inlineStr">
@@ -10599,6 +13589,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D599" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="600">
       <c r="A600" s="1" t="inlineStr">
@@ -10616,6 +13611,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D600" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="601">
       <c r="A601" s="1" t="inlineStr">
@@ -10633,6 +13633,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D601" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="602">
       <c r="A602" s="1" t="inlineStr">
@@ -10650,6 +13655,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D602" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="603">
       <c r="A603" s="1" t="inlineStr">
@@ -10667,6 +13677,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D603" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="1" t="inlineStr">
@@ -10684,6 +13699,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D604" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="1" t="inlineStr">
@@ -10701,6 +13721,11 @@
           <t>SIGNED</t>
         </is>
       </c>
+      <c r="D605" s="1" t="inlineStr">
+        <is>
+          <t>NOT_UPLOADED</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="1" t="inlineStr">
@@ -10715,6 +13740,11 @@
       </c>
       <c r="C606" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D606" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10732,6 +13762,11 @@
       </c>
       <c r="C607" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D607" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10749,6 +13784,11 @@
       </c>
       <c r="C608" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D608" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10766,6 +13806,11 @@
       </c>
       <c r="C609" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D609" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10783,6 +13828,11 @@
       </c>
       <c r="C610" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D610" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10800,6 +13850,11 @@
       </c>
       <c r="C611" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D611" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10817,6 +13872,11 @@
       </c>
       <c r="C612" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D612" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10834,6 +13894,11 @@
       </c>
       <c r="C613" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D613" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10851,6 +13916,11 @@
       </c>
       <c r="C614" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D614" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10868,6 +13938,11 @@
       </c>
       <c r="C615" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D615" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10885,6 +13960,11 @@
       </c>
       <c r="C616" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D616" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10902,6 +13982,11 @@
       </c>
       <c r="C617" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D617" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10919,6 +14004,11 @@
       </c>
       <c r="C618" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D618" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10936,6 +14026,11 @@
       </c>
       <c r="C619" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D619" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10953,6 +14048,11 @@
       </c>
       <c r="C620" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D620" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10970,6 +14070,11 @@
       </c>
       <c r="C621" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D621" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -10987,6 +14092,11 @@
       </c>
       <c r="C622" s="1" t="inlineStr">
         <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D622" s="1" t="inlineStr">
+        <is>
           <t>NOT_UPLOADED</t>
         </is>
       </c>
@@ -11003,6 +14113,11 @@
         </is>
       </c>
       <c r="C623" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D623" s="1" t="inlineStr">
         <is>
           <t>NOT_UPLOADED</t>
         </is>

--- a/data/db/subsystems.xlsx
+++ b/data/db/subsystems.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D623"/>
+  <dimension ref="A1:D653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14123,6 +14123,666 @@
         </is>
       </c>
     </row>
+    <row r="624">
+      <c r="A624" s="1" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="B624" s="1" t="inlineStr">
+        <is>
+          <t>3310-08-01</t>
+        </is>
+      </c>
+      <c r="C624" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D624" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" s="1" t="inlineStr">
+        <is>
+          <t>616</t>
+        </is>
+      </c>
+      <c r="B625" s="1" t="inlineStr">
+        <is>
+          <t>3310-09-01</t>
+        </is>
+      </c>
+      <c r="C625" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D625" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" s="1" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="B626" s="1" t="inlineStr">
+        <is>
+          <t>3310-17-03</t>
+        </is>
+      </c>
+      <c r="C626" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D626" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" s="1" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="B627" s="1" t="inlineStr">
+        <is>
+          <t>3510-01-01</t>
+        </is>
+      </c>
+      <c r="C627" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D627" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>619</t>
+        </is>
+      </c>
+      <c r="B628" s="1" t="inlineStr">
+        <is>
+          <t>3510-04-01</t>
+        </is>
+      </c>
+      <c r="C628" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D628" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" s="1" t="inlineStr">
+        <is>
+          <t>620</t>
+        </is>
+      </c>
+      <c r="B629" s="1" t="inlineStr">
+        <is>
+          <t>3530-01-04</t>
+        </is>
+      </c>
+      <c r="C629" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D629" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="1" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="B630" s="1" t="inlineStr">
+        <is>
+          <t>3410-06-02</t>
+        </is>
+      </c>
+      <c r="C630" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D630" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" s="1" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="B631" s="1" t="inlineStr">
+        <is>
+          <t>3420-15-02</t>
+        </is>
+      </c>
+      <c r="C631" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D631" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" s="1" t="inlineStr">
+        <is>
+          <t>623</t>
+        </is>
+      </c>
+      <c r="B632" s="1" t="inlineStr">
+        <is>
+          <t>3120-02-01</t>
+        </is>
+      </c>
+      <c r="C632" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D632" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="1" t="inlineStr">
+        <is>
+          <t>624</t>
+        </is>
+      </c>
+      <c r="B633" s="1" t="inlineStr">
+        <is>
+          <t>3110-02-03</t>
+        </is>
+      </c>
+      <c r="C633" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D633" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" s="1" t="inlineStr">
+        <is>
+          <t>625</t>
+        </is>
+      </c>
+      <c r="B634" s="1" t="inlineStr">
+        <is>
+          <t>2320-01-02</t>
+        </is>
+      </c>
+      <c r="C634" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D634" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" s="1" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="B635" s="1" t="inlineStr">
+        <is>
+          <t>2320-01-04</t>
+        </is>
+      </c>
+      <c r="C635" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D635" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" s="1" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="B636" s="1" t="inlineStr">
+        <is>
+          <t>2320-02-05</t>
+        </is>
+      </c>
+      <c r="C636" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D636" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" s="1" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="B637" s="1" t="inlineStr">
+        <is>
+          <t>2310-05-02</t>
+        </is>
+      </c>
+      <c r="C637" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D637" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" s="1" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="B638" s="1" t="inlineStr">
+        <is>
+          <t>2310-06-02</t>
+        </is>
+      </c>
+      <c r="C638" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D638" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="B639" s="1" t="inlineStr">
+        <is>
+          <t>2310-07-02</t>
+        </is>
+      </c>
+      <c r="C639" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D639" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" s="1" t="inlineStr">
+        <is>
+          <t>631</t>
+        </is>
+      </c>
+      <c r="B640" s="1" t="inlineStr">
+        <is>
+          <t>2120-01-02</t>
+        </is>
+      </c>
+      <c r="C640" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D640" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" s="1" t="inlineStr">
+        <is>
+          <t>632</t>
+        </is>
+      </c>
+      <c r="B641" s="1" t="inlineStr">
+        <is>
+          <t>2120-01-01</t>
+        </is>
+      </c>
+      <c r="C641" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D641" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" s="1" t="inlineStr">
+        <is>
+          <t>633</t>
+        </is>
+      </c>
+      <c r="B642" s="1" t="inlineStr">
+        <is>
+          <t>2110-90-09</t>
+        </is>
+      </c>
+      <c r="C642" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D642" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="1" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="B643" s="1" t="inlineStr">
+        <is>
+          <t>2100-01-03</t>
+        </is>
+      </c>
+      <c r="C643" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D643" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" s="1" t="inlineStr">
+        <is>
+          <t>635</t>
+        </is>
+      </c>
+      <c r="B644" s="1" t="inlineStr">
+        <is>
+          <t>2100-01-02</t>
+        </is>
+      </c>
+      <c r="C644" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D644" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" s="1" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="B645" s="1" t="inlineStr">
+        <is>
+          <t>3580-02-04</t>
+        </is>
+      </c>
+      <c r="C645" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D645" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="1" t="inlineStr">
+        <is>
+          <t>637</t>
+        </is>
+      </c>
+      <c r="B646" s="1" t="inlineStr">
+        <is>
+          <t>3580-07-01</t>
+        </is>
+      </c>
+      <c r="C646" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D646" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" s="1" t="inlineStr">
+        <is>
+          <t>638</t>
+        </is>
+      </c>
+      <c r="B647" s="1" t="inlineStr">
+        <is>
+          <t>3580-08-04</t>
+        </is>
+      </c>
+      <c r="C647" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D647" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="1" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="B648" s="1" t="inlineStr">
+        <is>
+          <t>2100-01-01</t>
+        </is>
+      </c>
+      <c r="C648" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D648" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" s="1" t="inlineStr">
+        <is>
+          <t>640</t>
+        </is>
+      </c>
+      <c r="B649" s="1" t="inlineStr">
+        <is>
+          <t>2191-50-09</t>
+        </is>
+      </c>
+      <c r="C649" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D649" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="B650" s="1" t="inlineStr">
+        <is>
+          <t>2114-90-01</t>
+        </is>
+      </c>
+      <c r="C650" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D650" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="1" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="B651" s="1" t="inlineStr">
+        <is>
+          <t>3191-90-01</t>
+        </is>
+      </c>
+      <c r="C651" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D651" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="1" t="inlineStr">
+        <is>
+          <t>643</t>
+        </is>
+      </c>
+      <c r="B652" s="1" t="inlineStr">
+        <is>
+          <t>3193-90-01</t>
+        </is>
+      </c>
+      <c r="C652" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D652" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="1" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="B653" s="1" t="inlineStr">
+        <is>
+          <t>3591-90-01</t>
+        </is>
+      </c>
+      <c r="C653" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D653" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/db/subsystems.xlsx
+++ b/data/db/subsystems.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D653"/>
+  <dimension ref="A1:D662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14783,6 +14783,204 @@
         </is>
       </c>
     </row>
+    <row r="654">
+      <c r="A654" s="1" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="B654" s="1" t="inlineStr">
+        <is>
+          <t>3310-21-02</t>
+        </is>
+      </c>
+      <c r="C654" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D654" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="1" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="B655" s="1" t="inlineStr">
+        <is>
+          <t>3210-01-01</t>
+        </is>
+      </c>
+      <c r="C655" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D655" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="1" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="B656" s="1" t="inlineStr">
+        <is>
+          <t>3410-02-02</t>
+        </is>
+      </c>
+      <c r="C656" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D656" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="1" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="B657" s="1" t="inlineStr">
+        <is>
+          <t>3410-11-03</t>
+        </is>
+      </c>
+      <c r="C657" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D657" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="1" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="B658" s="1" t="inlineStr">
+        <is>
+          <t>3410-16-02</t>
+        </is>
+      </c>
+      <c r="C658" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D658" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="1" t="inlineStr">
+        <is>
+          <t>649</t>
+        </is>
+      </c>
+      <c r="B659" s="1" t="inlineStr">
+        <is>
+          <t>3000-02-01</t>
+        </is>
+      </c>
+      <c r="C659" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D659" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="1" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B660" s="1" t="inlineStr">
+        <is>
+          <t>4110-03-01</t>
+        </is>
+      </c>
+      <c r="C660" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D660" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="B661" s="1" t="inlineStr">
+        <is>
+          <t>2110-01-01</t>
+        </is>
+      </c>
+      <c r="C661" s="1" t="inlineStr">
+        <is>
+          <t>SIGNED</t>
+        </is>
+      </c>
+      <c r="D661" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="1" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="B662" s="1" t="inlineStr">
+        <is>
+          <t>4130-90-01</t>
+        </is>
+      </c>
+      <c r="C662" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+      <c r="D662" s="1" t="inlineStr">
+        <is>
+          <t>NOT_SIGNED</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/db/subsystems.xlsx
+++ b/data/db/subsystems.xlsx
@@ -14984,7 +14984,7 @@
       </c>
       <c r="C662" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D662" s="2" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="C663" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D663" s="2" t="inlineStr">
@@ -15028,7 +15028,7 @@
       </c>
       <c r="C664" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D664" s="2" t="inlineStr">
@@ -15050,7 +15050,7 @@
       </c>
       <c r="C665" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D665" s="2" t="inlineStr">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="C666" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D666" s="2" t="inlineStr">
@@ -15094,7 +15094,7 @@
       </c>
       <c r="C667" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D667" s="2" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="C668" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D668" s="2" t="inlineStr">
@@ -15138,7 +15138,7 @@
       </c>
       <c r="C669" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D669" s="2" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="C670" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D670" s="2" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C671" s="2" t="inlineStr">
         <is>
-          <t>NOT_SIGNED</t>
+          <t>SIGNED</t>
         </is>
       </c>
       <c r="D671" s="2" t="inlineStr">
